--- a/data/trans_orig/P2A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2007</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>191802</t>
+          <t>192286</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>235359</t>
+          <t>237502</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>141029</t>
+          <t>139284</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>176513</t>
+          <t>174450</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>342615</t>
+          <t>343978</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>400174</t>
+          <t>400656</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,34%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>238417</t>
+          <t>236274</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281974</t>
+          <t>281490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130167</t>
+          <t>132230</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>165651</t>
+          <t>167396</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>380283</t>
+          <t>379801</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>437842</t>
+          <t>436479</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,93%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>154016</t>
+          <t>155476</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>191990</t>
+          <t>196732</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>186404</t>
+          <t>183715</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>224728</t>
+          <t>224588</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>353290</t>
+          <t>351475</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>408363</t>
+          <t>406946</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>174944</t>
+          <t>170202</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>212918</t>
+          <t>211458</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>147137</t>
+          <t>147277</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>185461</t>
+          <t>188150</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>330436</t>
+          <t>331853</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>385509</t>
+          <t>387324</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,43%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>240613</t>
+          <t>240876</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>286402</t>
+          <t>286019</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91260</t>
+          <t>91602</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115443</t>
+          <t>116031</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>340254</t>
+          <t>339052</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>394837</t>
+          <t>394902</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>255987</t>
+          <t>256370</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301776</t>
+          <t>301513</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52339</t>
+          <t>51751</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76522</t>
+          <t>76180</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>315334</t>
+          <t>315269</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>369917</t>
+          <t>371119</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,26%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>621357</t>
+          <t>621270</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>690996</t>
+          <t>691109</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>416748</t>
+          <t>417621</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>468604</t>
+          <t>472871</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1061191</t>
+          <t>1057520</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1145218</t>
+          <t>1144258</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,6%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>547338</t>
+          <t>547225</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>616977</t>
+          <t>617064</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>245681</t>
+          <t>241414</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>297537</t>
+          <t>296664</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>807402</t>
+          <t>808362</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>891429</t>
+          <t>895100</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,84%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>167009</t>
+          <t>166302</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>204436</t>
+          <t>205116</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>348514</t>
+          <t>342814</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>395389</t>
+          <t>393116</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>524890</t>
+          <t>525283</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>586371</t>
+          <t>582944</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,41%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>146119</t>
+          <t>145439</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>183546</t>
+          <t>184253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>173363</t>
+          <t>175636</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>220238</t>
+          <t>225938</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>332936</t>
+          <t>336363</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>394417</t>
+          <t>394024</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>42,86%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66609</t>
+          <t>66992</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>96195</t>
+          <t>97671</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>841811</t>
+          <t>840460</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>905163</t>
+          <t>903894</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>919220</t>
+          <t>918133</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>993202</t>
+          <t>995449</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,35%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>202006</t>
+          <t>200530</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>231592</t>
+          <t>231209</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>343597</t>
+          <t>344866</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>406949</t>
+          <t>408300</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>553758</t>
+          <t>551511</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>627740</t>
+          <t>628827</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,65%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1518293</t>
+          <t>1520192</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1637052</t>
+          <t>1630168</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2101418</t>
+          <t>2105467</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2213359</t>
+          <t>2214502</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3648345</t>
+          <t>3639230</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3810487</t>
+          <t>3802255</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,19%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1633138</t>
+          <t>1640022</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1751897</t>
+          <t>1749998</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1164765</t>
+          <t>1163622</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1276706</t>
+          <t>1272657</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2837827</t>
+          <t>2846059</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2999969</t>
+          <t>3009084</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2012</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>203237</t>
+          <t>201787</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>247046</t>
+          <t>245575</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>149241</t>
+          <t>149005</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>185908</t>
+          <t>187352</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>358096</t>
+          <t>362957</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>419060</t>
+          <t>418163</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,63%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>190165</t>
+          <t>191636</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>233974</t>
+          <t>235424</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>128546</t>
+          <t>127102</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>165213</t>
+          <t>165449</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>332605</t>
+          <t>333502</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>393569</t>
+          <t>388708</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>51,71%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>199372</t>
+          <t>203156</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>245396</t>
+          <t>247500</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>192503</t>
+          <t>192141</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>231109</t>
+          <t>229626</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>404832</t>
+          <t>410190</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>466164</t>
+          <t>466156</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,59%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>173401</t>
+          <t>171297</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>219425</t>
+          <t>215641</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>106902</t>
+          <t>108385</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>145508</t>
+          <t>145870</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>290644</t>
+          <t>290652</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>351976</t>
+          <t>346618</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>45,8%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>343711</t>
+          <t>346914</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>395104</t>
+          <t>395833</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>169207</t>
+          <t>167569</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>198649</t>
+          <t>198250</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>525739</t>
+          <t>526135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>585711</t>
+          <t>585905</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,87%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>234311</t>
+          <t>233582</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>285704</t>
+          <t>282501</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61480</t>
+          <t>61879</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90922</t>
+          <t>92560</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>303833</t>
+          <t>303639</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>363805</t>
+          <t>363409</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,85%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>645561</t>
+          <t>644991</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>712902</t>
+          <t>714982</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,47 +4412,47 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>61,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>500114</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>471541</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>526086</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>65,23%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>61,51%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>462</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>500114</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>473131</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>525345</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>65,23%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>61,71%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1133020</t>
+          <t>1136997</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1224203</t>
+          <t>1227122</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,72%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>446107</t>
+          <t>444027</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>513448</t>
+          <t>514018</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,49 +4525,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>38,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>44,35%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>266543</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>240571</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>295116</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>34,77%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>31,38%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>38,49%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>44,3%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>266543</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>241312</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>293526</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>34,77%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>31,48%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>38,29%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>692</t>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>701464</t>
+          <t>698545</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>792647</t>
+          <t>788670</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>277750</t>
+          <t>279756</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>321897</t>
+          <t>324649</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>546242</t>
+          <t>544832</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>595330</t>
+          <t>596059</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>834944</t>
+          <t>837628</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>906852</t>
+          <t>905339</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,63%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,17%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>188699</t>
+          <t>185947</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>232846</t>
+          <t>230840</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>166192</t>
+          <t>165463</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215280</t>
+          <t>216690</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>365266</t>
+          <t>366779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>437174</t>
+          <t>434490</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,15%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87125</t>
+          <t>87631</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>117901</t>
+          <t>120710</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>785501</t>
+          <t>793011</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>846563</t>
+          <t>848115</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>886750</t>
+          <t>885439</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>961567</t>
+          <t>957364</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,56%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>148981</t>
+          <t>146172</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>179757</t>
+          <t>179251</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>262788</t>
+          <t>261236</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>323850</t>
+          <t>316340</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>414666</t>
+          <t>418869</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>489483</t>
+          <t>490794</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1842873</t>
+          <t>1844622</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1959961</t>
+          <t>1964732</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2404377</t>
+          <t>2398654</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2508480</t>
+          <t>2511239</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4275508</t>
+          <t>4276637</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4437010</t>
+          <t>4435777</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,62%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1461949</t>
+          <t>1457178</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1579037</t>
+          <t>1577288</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1041645</t>
+          <t>1038886</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1145748</t>
+          <t>1151471</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2535025</t>
+          <t>2536258</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2696527</t>
+          <t>2695398</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2016</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>177541</t>
+          <t>173838</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>219488</t>
+          <t>218487</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>163827</t>
+          <t>163530</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>201646</t>
+          <t>200790</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>350513</t>
+          <t>352197</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>409503</t>
+          <t>409242</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>209604</t>
+          <t>210605</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>251551</t>
+          <t>255254</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>145409</t>
+          <t>146265</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>183228</t>
+          <t>183525</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>366644</t>
+          <t>366905</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>425634</t>
+          <t>423950</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,62%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>167513</t>
+          <t>164790</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>205787</t>
+          <t>205027</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>170736</t>
+          <t>172152</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>209356</t>
+          <t>210874</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>349031</t>
+          <t>349641</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>403236</t>
+          <t>402772</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>53,74%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>171440</t>
+          <t>172200</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>209714</t>
+          <t>212437</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>162917</t>
+          <t>161399</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>201537</t>
+          <t>200121</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>346264</t>
+          <t>346728</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>400469</t>
+          <t>399859</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,35%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>283037</t>
+          <t>283873</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>329155</t>
+          <t>327344</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97436</t>
+          <t>98064</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>121321</t>
+          <t>122223</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>390029</t>
+          <t>389021</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>442497</t>
+          <t>442870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,37%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>192759</t>
+          <t>194570</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>238877</t>
+          <t>238041</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44802</t>
+          <t>43900</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68687</t>
+          <t>68059</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>245539</t>
+          <t>245166</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>298007</t>
+          <t>299015</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,46%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>596325</t>
+          <t>596866</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>666369</t>
+          <t>667128</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>438713</t>
+          <t>438178</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>494556</t>
+          <t>496588</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1049466</t>
+          <t>1051499</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1138850</t>
+          <t>1142222</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,82%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>483269</t>
+          <t>482510</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>553313</t>
+          <t>552772</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>331320</t>
+          <t>329288</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387163</t>
+          <t>387698</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>836664</t>
+          <t>833292</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>926048</t>
+          <t>924015</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,77%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>327506</t>
+          <t>323100</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>377192</t>
+          <t>374586</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>518830</t>
+          <t>517737</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>564926</t>
+          <t>565542</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,52%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>855515</t>
+          <t>857658</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>926422</t>
+          <t>928382</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,32%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>243514</t>
+          <t>246120</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>293200</t>
+          <t>297606</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>173318</t>
+          <t>172702</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>219414</t>
+          <t>220507</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>432528</t>
+          <t>430568</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>503435</t>
+          <t>501292</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,89%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86071</t>
+          <t>84162</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>116931</t>
+          <t>115095</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>723755</t>
+          <t>724648</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>784376</t>
+          <t>785705</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>821220</t>
+          <t>821166</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>894521</t>
+          <t>893120</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,23%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170214</t>
+          <t>172050</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>201074</t>
+          <t>202983</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>297649</t>
+          <t>296320</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>358270</t>
+          <t>357377</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>474649</t>
+          <t>476050</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>547950</t>
+          <t>548004</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1713854</t>
+          <t>1716627</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1833621</t>
+          <t>1831175</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2186543</t>
+          <t>2187468</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2306008</t>
+          <t>2303831</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3936666</t>
+          <t>3935775</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4103094</t>
+          <t>4101340</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1552101</t>
+          <t>1554547</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1671868</t>
+          <t>1669095</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1225588</t>
+          <t>1227765</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1345053</t>
+          <t>1344128</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2814224</t>
+          <t>2815978</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2980652</t>
+          <t>2981543</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2023</t>
+          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>170001</t>
+          <t>170572</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>215048</t>
+          <t>214362</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>156945</t>
+          <t>157562</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>192883</t>
+          <t>193581</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>339687</t>
+          <t>335320</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>394739</t>
+          <t>394963</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>290164</t>
+          <t>290850</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>335211</t>
+          <t>334640</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>254584</t>
+          <t>253886</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>290522</t>
+          <t>289905</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>557940</t>
+          <t>557716</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>612992</t>
+          <t>617359</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,8%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>136801</t>
+          <t>137056</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>179251</t>
+          <t>180291</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>123958</t>
+          <t>123857</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>154911</t>
+          <t>156571</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>273675</t>
+          <t>274535</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>323773</t>
+          <t>324329</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>272962</t>
+          <t>271922</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>315412</t>
+          <t>315157</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>227669</t>
+          <t>226009</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>258622</t>
+          <t>258723</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>511020</t>
+          <t>510464</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>561118</t>
+          <t>560258</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,11%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61613</t>
+          <t>71716</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>279876</t>
+          <t>281349</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74293</t>
+          <t>75065</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95440</t>
+          <t>96150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>106677</t>
+          <t>122511</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>372205</t>
+          <t>370713</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,39%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>388388</t>
+          <t>386915</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>606651</t>
+          <t>596548</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71471</t>
+          <t>70761</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92618</t>
+          <t>91846</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>462970</t>
+          <t>464462</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>728498</t>
+          <t>712664</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>85,33%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>420541</t>
+          <t>417797</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>491085</t>
+          <t>488162</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>409252</t>
+          <t>410481</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>747461</t>
+          <t>722863</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>861433</t>
+          <t>862901</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1271343</t>
+          <t>1320838</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>65,62%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>543734</t>
+          <t>546657</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>614278</t>
+          <t>617022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>230633</t>
+          <t>255231</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>568842</t>
+          <t>567613</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>741569</t>
+          <t>692074</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1151479</t>
+          <t>1150011</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,13%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>211359</t>
+          <t>209552</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>257141</t>
+          <t>255959</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>290456</t>
+          <t>307054</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>458798</t>
+          <t>464493</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>528375</t>
+          <t>527387</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>693161</t>
+          <t>693123</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,65%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>217905</t>
+          <t>219087</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>263687</t>
+          <t>265494</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>382537</t>
+          <t>376842</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>550879</t>
+          <t>534281</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>623220</t>
+          <t>623258</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>788006</t>
+          <t>788994</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,94%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>45426</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>90578</t>
+          <t>94059</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>373170</t>
+          <t>371159</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>424200</t>
+          <t>423221</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>428121</t>
+          <t>426493</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>500340</t>
+          <t>499917</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,9%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>149929</t>
+          <t>146448</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>197420</t>
+          <t>195081</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>337171</t>
+          <t>338150</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>388201</t>
+          <t>390212</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>501538</t>
+          <t>501961</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>573757</t>
+          <t>575385</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>994699</t>
+          <t>1023600</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1394556</t>
+          <t>1393530</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1586693</t>
+          <t>1600943</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2101036</t>
+          <t>2078292</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2695422</t>
+          <t>2705141</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3337636</t>
+          <t>3331369</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,91%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1981504</t>
+          <t>1982530</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2381361</t>
+          <t>2352460</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1476722</t>
+          <t>1499466</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1991065</t>
+          <t>1976815</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3616182</t>
+          <t>3622449</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4258396</t>
+          <t>4248677</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>192286</t>
+          <t>190534</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>237502</t>
+          <t>236262</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>139284</t>
+          <t>138134</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>174450</t>
+          <t>174960</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>343978</t>
+          <t>339089</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>400656</t>
+          <t>399707</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,21%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>236274</t>
+          <t>237514</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281490</t>
+          <t>283242</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>132230</t>
+          <t>131720</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>167396</t>
+          <t>168546</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>379801</t>
+          <t>380750</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>436479</t>
+          <t>441368</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,55%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>155476</t>
+          <t>154671</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>196732</t>
+          <t>193353</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>183715</t>
+          <t>184657</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>224588</t>
+          <t>223901</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>351475</t>
+          <t>352908</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>406946</t>
+          <t>408506</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,29%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>170202</t>
+          <t>173581</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>211458</t>
+          <t>212263</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>147277</t>
+          <t>147964</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>188150</t>
+          <t>187208</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>331853</t>
+          <t>330293</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>387324</t>
+          <t>385891</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,23%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>240876</t>
+          <t>239911</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>286019</t>
+          <t>288471</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91602</t>
+          <t>91744</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116031</t>
+          <t>116767</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>339052</t>
+          <t>341326</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>394902</t>
+          <t>393436</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,4%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>256370</t>
+          <t>253918</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301513</t>
+          <t>302478</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51751</t>
+          <t>51015</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76180</t>
+          <t>76038</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>315269</t>
+          <t>316735</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>371119</t>
+          <t>368845</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>51,94%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>621270</t>
+          <t>622050</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>691109</t>
+          <t>689868</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>417621</t>
+          <t>420780</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>472871</t>
+          <t>471240</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1057520</t>
+          <t>1053709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1144258</t>
+          <t>1143685</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,57%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>547225</t>
+          <t>548466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>617064</t>
+          <t>616284</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>241414</t>
+          <t>243045</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>296664</t>
+          <t>293505</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>808362</t>
+          <t>808935</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>895100</t>
+          <t>898911</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,04%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>166302</t>
+          <t>167185</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>205116</t>
+          <t>204220</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>342814</t>
+          <t>350061</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>393116</t>
+          <t>396199</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>525283</t>
+          <t>527323</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>582944</t>
+          <t>587119</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,87%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>145439</t>
+          <t>146335</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>184253</t>
+          <t>183370</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>175636</t>
+          <t>172553</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>225938</t>
+          <t>218691</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>336363</t>
+          <t>332188</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>394024</t>
+          <t>391984</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,64%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>66992</t>
+          <t>66693</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97671</t>
+          <t>97030</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>840460</t>
+          <t>839657</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>903894</t>
+          <t>903109</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>918133</t>
+          <t>914031</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>995449</t>
+          <t>990390</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,02%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200530</t>
+          <t>201171</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>231209</t>
+          <t>231508</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>344866</t>
+          <t>345651</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>408300</t>
+          <t>409103</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>551511</t>
+          <t>556570</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>628827</t>
+          <t>632929</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1520192</t>
+          <t>1517361</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1630168</t>
+          <t>1633135</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2105467</t>
+          <t>2091553</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2214502</t>
+          <t>2211876</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3639230</t>
+          <t>3650657</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3802255</t>
+          <t>3812577</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1640022</t>
+          <t>1637055</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1749998</t>
+          <t>1752829</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1163622</t>
+          <t>1166248</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1272657</t>
+          <t>1286571</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2846059</t>
+          <t>2835737</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3009084</t>
+          <t>2997657</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,09%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>201787</t>
+          <t>202354</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>245575</t>
+          <t>245415</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>149005</t>
+          <t>147778</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>187352</t>
+          <t>186100</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>362957</t>
+          <t>361912</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>418163</t>
+          <t>420084</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,89%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>191636</t>
+          <t>191796</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>235424</t>
+          <t>234857</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127102</t>
+          <t>128354</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>165449</t>
+          <t>166676</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>333502</t>
+          <t>331581</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>388708</t>
+          <t>389753</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,85%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>203156</t>
+          <t>202333</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>247500</t>
+          <t>246816</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>192141</t>
+          <t>192813</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229626</t>
+          <t>229448</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>410190</t>
+          <t>407832</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>466156</t>
+          <t>466832</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,68%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>171297</t>
+          <t>171981</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>215641</t>
+          <t>216464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>108385</t>
+          <t>108563</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>145870</t>
+          <t>145198</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>290652</t>
+          <t>289976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>346618</t>
+          <t>348976</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>46,11%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>346914</t>
+          <t>343465</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>395833</t>
+          <t>395495</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>167569</t>
+          <t>168584</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>198250</t>
+          <t>199359</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>526135</t>
+          <t>524861</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>585905</t>
+          <t>583345</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>233582</t>
+          <t>233920</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282501</t>
+          <t>285950</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61879</t>
+          <t>60770</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92560</t>
+          <t>91545</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>303639</t>
+          <t>306199</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>363409</t>
+          <t>364683</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,0%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>644991</t>
+          <t>646305</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>714982</t>
+          <t>717409</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>471541</t>
+          <t>471909</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>526086</t>
+          <t>527772</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1136997</t>
+          <t>1137231</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1227122</t>
+          <t>1223385</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,53%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>444027</t>
+          <t>441600</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>514018</t>
+          <t>512704</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>240571</t>
+          <t>238885</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>295116</t>
+          <t>294748</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>698545</t>
+          <t>702282</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>788670</t>
+          <t>788436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>279756</t>
+          <t>279151</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>324649</t>
+          <t>322193</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>544832</t>
+          <t>544120</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>596059</t>
+          <t>593920</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>837628</t>
+          <t>837216</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>905339</t>
+          <t>906927</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>185947</t>
+          <t>188403</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>230840</t>
+          <t>231445</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>165463</t>
+          <t>167602</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216690</t>
+          <t>217402</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>366779</t>
+          <t>365191</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>434490</t>
+          <t>434902</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87631</t>
+          <t>85371</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>120710</t>
+          <t>119380</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>793011</t>
+          <t>788529</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>848115</t>
+          <t>847837</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>885439</t>
+          <t>884491</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>957364</t>
+          <t>956616</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,51%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>146172</t>
+          <t>147502</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>179251</t>
+          <t>181511</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261236</t>
+          <t>261514</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>316340</t>
+          <t>320822</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>418869</t>
+          <t>419617</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>490794</t>
+          <t>491742</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1844622</t>
+          <t>1845051</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1964732</t>
+          <t>1960755</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2398654</t>
+          <t>2398225</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2511239</t>
+          <t>2513983</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4276637</t>
+          <t>4272334</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4435777</t>
+          <t>4436189</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,63%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1457178</t>
+          <t>1461155</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1577288</t>
+          <t>1576859</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1038886</t>
+          <t>1036142</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1151471</t>
+          <t>1151900</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2536258</t>
+          <t>2535846</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2695398</t>
+          <t>2699701</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,72%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>173838</t>
+          <t>175348</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>218487</t>
+          <t>218297</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>163530</t>
+          <t>163414</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>200790</t>
+          <t>200511</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>352197</t>
+          <t>348601</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>409242</t>
+          <t>405633</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,26%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>210605</t>
+          <t>210795</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>255254</t>
+          <t>253744</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>146544</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>183525</t>
+          <t>183641</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>366905</t>
+          <t>370514</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>423950</t>
+          <t>427546</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>55,09%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>164790</t>
+          <t>168083</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>205027</t>
+          <t>208188</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>172152</t>
+          <t>171966</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>210874</t>
+          <t>209394</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>349641</t>
+          <t>348104</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>402772</t>
+          <t>404844</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>54,02%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172200</t>
+          <t>169039</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>212437</t>
+          <t>209144</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>161399</t>
+          <t>162879</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>200121</t>
+          <t>200307</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>346728</t>
+          <t>344656</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>399859</t>
+          <t>401396</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,56%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>283873</t>
+          <t>282800</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>327344</t>
+          <t>328212</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98064</t>
+          <t>97502</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122223</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>389021</t>
+          <t>391716</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>442870</t>
+          <t>443236</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,42%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>194570</t>
+          <t>193702</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>238041</t>
+          <t>239114</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43900</t>
+          <t>44283</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68059</t>
+          <t>68621</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>245166</t>
+          <t>244800</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>299015</t>
+          <t>296320</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,07%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>596866</t>
+          <t>600234</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>667128</t>
+          <t>665943</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>438178</t>
+          <t>438547</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>496588</t>
+          <t>494852</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1051499</t>
+          <t>1053801</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1142222</t>
+          <t>1141810</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>482510</t>
+          <t>483695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>552772</t>
+          <t>549404</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>329288</t>
+          <t>331024</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387698</t>
+          <t>387329</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>833292</t>
+          <t>833704</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>924015</t>
+          <t>921713</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,66%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>323100</t>
+          <t>327048</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>374586</t>
+          <t>374945</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>517737</t>
+          <t>519143</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>565542</t>
+          <t>565599</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>857658</t>
+          <t>855131</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>928382</t>
+          <t>928339</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,31%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>246120</t>
+          <t>245761</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>297606</t>
+          <t>293658</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>172702</t>
+          <t>172645</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>220507</t>
+          <t>219101</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>430568</t>
+          <t>430611</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>501292</t>
+          <t>503819</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84162</t>
+          <t>83899</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>115095</t>
+          <t>115858</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>724648</t>
+          <t>725855</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>785705</t>
+          <t>784248</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>821166</t>
+          <t>818813</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>893120</t>
+          <t>894184</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,31%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>172050</t>
+          <t>171287</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>202983</t>
+          <t>203246</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>296320</t>
+          <t>297777</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>357377</t>
+          <t>356170</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>476050</t>
+          <t>474986</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>548004</t>
+          <t>550357</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,2%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1716627</t>
+          <t>1714948</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1831175</t>
+          <t>1832045</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2187468</t>
+          <t>2188861</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2303831</t>
+          <t>2305965</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3935775</t>
+          <t>3936735</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4101340</t>
+          <t>4112446</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,45%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1554547</t>
+          <t>1553677</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1669095</t>
+          <t>1670774</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1227765</t>
+          <t>1225631</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1344128</t>
+          <t>1342735</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2815978</t>
+          <t>2804872</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2981543</t>
+          <t>2980583</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,09%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>191435</t>
+          <t>207276</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>170572</t>
+          <t>183306</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>214362</t>
+          <t>229439</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>175364</t>
+          <t>191858</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>157562</t>
+          <t>174971</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>193581</t>
+          <t>212158</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>366799</t>
+          <t>399134</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>335320</t>
+          <t>371026</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>394963</t>
+          <t>430300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,41%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>313777</t>
+          <t>343342</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>290850</t>
+          <t>321179</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>334640</t>
+          <t>367312</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>272103</t>
+          <t>296553</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>253886</t>
+          <t>276253</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>289905</t>
+          <t>313440</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>585880</t>
+          <t>639895</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>557716</t>
+          <t>608729</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>617359</t>
+          <t>668003</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,29%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>159072</t>
+          <t>165889</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>137056</t>
+          <t>144852</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>180291</t>
+          <t>186745</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>139461</t>
+          <t>152168</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>123857</t>
+          <t>135165</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>156571</t>
+          <t>168913</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>298533</t>
+          <t>318058</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>274535</t>
+          <t>292580</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>324329</t>
+          <t>345191</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,09%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>293141</t>
+          <t>317323</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>271922</t>
+          <t>296467</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>315157</t>
+          <t>338360</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,69%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>243119</t>
+          <t>270975</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>226009</t>
+          <t>254230</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>258723</t>
+          <t>287978</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>536260</t>
+          <t>588297</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>510464</t>
+          <t>561164</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>560258</t>
+          <t>613775</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,72%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>172241</t>
+          <t>186247</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71716</t>
+          <t>164559</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>281349</t>
+          <t>207282</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>84850</t>
+          <t>94440</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75065</t>
+          <t>83145</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96150</t>
+          <t>105943</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>257092</t>
+          <t>280687</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>122511</t>
+          <t>259004</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>370713</t>
+          <t>306811</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>46,55%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>496023</t>
+          <t>285365</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>386915</t>
+          <t>264330</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>596548</t>
+          <t>307053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>82061</t>
+          <t>93057</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70761</t>
+          <t>81554</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91846</t>
+          <t>104352</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>578083</t>
+          <t>378422</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>464462</t>
+          <t>352298</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>712664</t>
+          <t>400105</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>60,7%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>455146</t>
+          <t>485299</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>417797</t>
+          <t>451842</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>488162</t>
+          <t>521739</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>537496</t>
+          <t>365991</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>410481</t>
+          <t>341186</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>722863</t>
+          <t>392478</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>992642</t>
+          <t>851289</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>862901</t>
+          <t>810241</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1320838</t>
+          <t>895226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>579673</t>
+          <t>646544</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>546657</t>
+          <t>610104</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>617022</t>
+          <t>680001</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>440598</t>
+          <t>495220</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>255231</t>
+          <t>468733</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>567613</t>
+          <t>520025</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1020270</t>
+          <t>1141765</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>692074</t>
+          <t>1097828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1150011</t>
+          <t>1182813</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>59,35%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>232177</t>
+          <t>249539</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>209552</t>
+          <t>222774</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>255959</t>
+          <t>273929</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>405600</t>
+          <t>441450</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>307054</t>
+          <t>416351</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>464493</t>
+          <t>464140</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>637777</t>
+          <t>690989</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>527387</t>
+          <t>655589</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>693123</t>
+          <t>723703</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>51,74%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>242869</t>
+          <t>318425</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>219087</t>
+          <t>294035</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>265494</t>
+          <t>345190</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>435735</t>
+          <t>389400</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>376842</t>
+          <t>366710</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>534281</t>
+          <t>414499</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>678604</t>
+          <t>707825</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>623258</t>
+          <t>675111</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>788994</t>
+          <t>743225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>53,13%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>65180</t>
+          <t>59841</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45426</t>
+          <t>42796</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>94059</t>
+          <t>81619</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>398207</t>
+          <t>437357</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>371159</t>
+          <t>407342</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>423221</t>
+          <t>464035</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,22 +10418,22 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>463386</t>
+          <t>497199</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>426493</t>
+          <t>460351</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>499917</t>
+          <t>533897</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,37%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>175327</t>
+          <t>177387</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>146448</t>
+          <t>155609</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>195081</t>
+          <t>194432</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>363164</t>
+          <t>406924</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>338150</t>
+          <t>380246</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>390212</t>
+          <t>436939</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,27 +10531,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>538492</t>
+          <t>584310</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>501961</t>
+          <t>547612</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>575385</t>
+          <t>621158</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1275250</t>
+          <t>1354092</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1023600</t>
+          <t>1286935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1393530</t>
+          <t>1412183</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1740979</t>
+          <t>1683263</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1600943</t>
+          <t>1631368</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2078292</t>
+          <t>1737254</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3016229</t>
+          <t>3037355</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2705141</t>
+          <t>2955531</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3331369</t>
+          <t>3118718</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>44,06%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2100810</t>
+          <t>2088384</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1982530</t>
+          <t>2030293</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2352460</t>
+          <t>2155541</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1836779</t>
+          <t>1952130</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1499466</t>
+          <t>1898139</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1976815</t>
+          <t>2004025</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3937589</t>
+          <t>4040514</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3622449</t>
+          <t>3959151</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4248677</t>
+          <t>4122338</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>58,24%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con alguna condición, enfermedad crónica o limitación en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna condición, enfermedad crónica o limitación en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
